--- a/registration_forms/048_multi_family_housing_summit_registration_form--registration_forms.xlsx
+++ b/registration_forms/048_multi_family_housing_summit_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,8 +911,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -940,12 +940,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'attendee'}</t>
+          <t>attendee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Attendee'}</t>
+          <t>Attendee</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'speaker'}</t>
+          <t>speaker</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Speaker'}</t>
+          <t>Speaker</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'organizer'}</t>
+          <t>organizer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Organizer'}</t>
+          <t>Organizer</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'on-site'}</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'On-site'}</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
